--- a/data/supplementary_information/1.Phenotype_categories.xlsx
+++ b/data/supplementary_information/1.Phenotype_categories.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/supplementary_information/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273E5018-B0D1-264A-91F7-E4915E1557E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B4BBF8-C463-F849-BF1F-8DBDA0C98718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HN_LN_expected_traits" sheetId="1" r:id="rId1"/>
@@ -37,69 +37,12 @@
     <t>Architecture</t>
   </si>
   <si>
-    <t>branchInternodeLength</t>
-  </si>
-  <si>
-    <t>plantHeight</t>
-  </si>
-  <si>
-    <t>primaryBranchNumber</t>
-  </si>
-  <si>
-    <t>tillersPerPlant</t>
-  </si>
-  <si>
     <t>Developmental</t>
   </si>
   <si>
-    <t>daysToFlower</t>
-  </si>
-  <si>
-    <t>extantLeafNumber</t>
-  </si>
-  <si>
-    <t>flagLeafLength</t>
-  </si>
-  <si>
-    <t>flagLeafWidth</t>
-  </si>
-  <si>
-    <t>leafAngleStandardDeviation</t>
-  </si>
-  <si>
-    <t>medianLeafAngle</t>
-  </si>
-  <si>
-    <t>stemDiameterLower</t>
-  </si>
-  <si>
-    <t>stemDiameterUpper</t>
-  </si>
-  <si>
-    <t>thirdLeafLength</t>
-  </si>
-  <si>
-    <t>thirdLeafWidth</t>
-  </si>
-  <si>
     <t>Panicle</t>
   </si>
   <si>
-    <t>panicleGrainWeight</t>
-  </si>
-  <si>
-    <t>paniclesPerPlot</t>
-  </si>
-  <si>
-    <t>rachisDiameterLower</t>
-  </si>
-  <si>
-    <t>rachisDiameterUpper</t>
-  </si>
-  <si>
-    <t>rachisLength</t>
-  </si>
-  <si>
     <t>BIL</t>
   </si>
   <si>
@@ -155,6 +98,63 @@
   </si>
   <si>
     <t>RL</t>
+  </si>
+  <si>
+    <t>Branch internode length</t>
+  </si>
+  <si>
+    <t>Plant height</t>
+  </si>
+  <si>
+    <t>Primary branch number</t>
+  </si>
+  <si>
+    <t>Tillers per plant</t>
+  </si>
+  <si>
+    <t>Days to flower</t>
+  </si>
+  <si>
+    <t>Extant leaf number</t>
+  </si>
+  <si>
+    <t>Flag leaf length</t>
+  </si>
+  <si>
+    <t>Flag leaf width</t>
+  </si>
+  <si>
+    <t>Leaf angle standard deviation</t>
+  </si>
+  <si>
+    <t>Median leaf angle</t>
+  </si>
+  <si>
+    <t>Stem diameter lower</t>
+  </si>
+  <si>
+    <t>Stem diameter upper</t>
+  </si>
+  <si>
+    <t>Third leaf length</t>
+  </si>
+  <si>
+    <t>Third leaf width</t>
+  </si>
+  <si>
+    <t>Panicle grain weight</t>
+  </si>
+  <si>
+    <t>Panicles per plot</t>
+  </si>
+  <si>
+    <t>Rachis diameter lower</t>
+  </si>
+  <si>
+    <t>Rachis diameter upper</t>
+  </si>
+  <si>
+    <t>Rachis length</t>
   </si>
 </sst>
 </file>
@@ -513,7 +513,7 @@
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -535,13 +535,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>2020</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -549,13 +549,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>2020</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -563,13 +563,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>2021</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -577,13 +577,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>2020</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -591,265 +591,265 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>2020</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>2020</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>2021</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>2020</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>2020</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>2020</v>
+      </c>
+      <c r="D11" t="s">
         <v>13</v>
-      </c>
-      <c r="C11">
-        <v>2020</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>2020</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>2020</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>2020</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>2021</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>2020</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>2021</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C18">
         <v>2020</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <v>2020</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>2020</v>
+      </c>
+      <c r="D20" t="s">
         <v>21</v>
-      </c>
-      <c r="C20">
-        <v>2020</v>
-      </c>
-      <c r="D20" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21">
+        <v>2020</v>
+      </c>
+      <c r="D21" t="s">
         <v>22</v>
-      </c>
-      <c r="C21">
-        <v>2020</v>
-      </c>
-      <c r="D21" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22">
+        <v>2020</v>
+      </c>
+      <c r="D22" t="s">
         <v>23</v>
-      </c>
-      <c r="C22">
-        <v>2020</v>
-      </c>
-      <c r="D22" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23">
+        <v>2020</v>
+      </c>
+      <c r="D23" t="s">
         <v>24</v>
-      </c>
-      <c r="C23">
-        <v>2020</v>
-      </c>
-      <c r="D23" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24">
+        <v>2020</v>
+      </c>
+      <c r="D24" t="s">
         <v>25</v>
-      </c>
-      <c r="C24">
-        <v>2020</v>
-      </c>
-      <c r="D24" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/supplementary_information/1.Phenotype_categories.xlsx
+++ b/data/supplementary_information/1.Phenotype_categories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/supplementary_information/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B4BBF8-C463-F849-BF1F-8DBDA0C98718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3D2234-2728-0D42-8D27-73D8C077838A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="46">
   <si>
     <t>category</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>Rachis length</t>
+  </si>
+  <si>
+    <t>Table S1. The full list of traits collected from filed and organized by Category</t>
   </si>
 </sst>
 </file>
@@ -198,11 +201,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -516,32 +520,26 @@
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2">
-        <v>2020</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -549,13 +547,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>2020</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -566,7 +564,7 @@
         <v>27</v>
       </c>
       <c r="C4">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -577,13 +575,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -591,27 +589,27 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>2020</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>2020</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -622,7 +620,7 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -633,13 +631,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -647,13 +645,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>2020</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -661,13 +659,13 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>2020</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -675,13 +673,13 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>2020</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -689,13 +687,13 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>2020</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -703,13 +701,13 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>2020</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -720,7 +718,7 @@
         <v>36</v>
       </c>
       <c r="C15">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -731,13 +729,13 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -748,7 +746,7 @@
         <v>37</v>
       </c>
       <c r="C17">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -759,13 +757,13 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -773,27 +771,27 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>2020</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>2020</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -801,13 +799,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21">
         <v>2020</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -815,13 +813,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22">
         <v>2020</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -829,13 +827,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23">
         <v>2020</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -843,12 +841,26 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24">
+        <v>2020</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
         <v>44</v>
       </c>
-      <c r="C24">
-        <v>2020</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C25">
+        <v>2020</v>
+      </c>
+      <c r="D25" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/supplementary_information/1.Phenotype_categories.xlsx
+++ b/data/supplementary_information/1.Phenotype_categories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/supplementary_information/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3D2234-2728-0D42-8D27-73D8C077838A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67BCF93C-9AAD-9448-A007-AC67560A2B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,7 +206,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,13 +520,10 @@
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">

--- a/data/supplementary_information/1.Phenotype_categories.xlsx
+++ b/data/supplementary_information/1.Phenotype_categories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/supplementary_information/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67BCF93C-9AAD-9448-A007-AC67560A2B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D94A2A-5314-A741-8280-413786211A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,18 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="46">
   <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>trait</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>plot_label</t>
-  </si>
-  <si>
     <t>Architecture</t>
   </si>
   <si>
@@ -158,6 +146,18 @@
   </si>
   <si>
     <t>Table S1. The full list of traits collected from filed and organized by Category</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Trait</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Plot_label</t>
   </si>
 </sst>
 </file>
@@ -189,7 +189,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -197,16 +197,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,343 +541,343 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3">
-        <v>2020</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>2020</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5">
-        <v>2021</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6">
-        <v>2020</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7">
-        <v>2020</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>2020</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9">
-        <v>2021</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10">
-        <v>2020</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11">
-        <v>2020</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12">
-        <v>2020</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13">
-        <v>2020</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14">
-        <v>2020</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="B21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C15">
-        <v>2020</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C21" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16">
-        <v>2021</v>
-      </c>
-      <c r="D16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C17">
-        <v>2020</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C22" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18">
-        <v>2021</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C19">
-        <v>2020</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C23" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C20">
-        <v>2020</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C24" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C21">
-        <v>2020</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C25" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22">
-        <v>2020</v>
-      </c>
-      <c r="D22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23">
-        <v>2020</v>
-      </c>
-      <c r="D23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24">
-        <v>2020</v>
-      </c>
-      <c r="D24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25">
-        <v>2020</v>
-      </c>
-      <c r="D25" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
